--- a/04_Output/rC_DG.xlsx
+++ b/04_Output/rC_DG.xlsx
@@ -10,18 +10,17 @@
     <sheet name="15" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="5" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5.4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5a" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="6a" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="7" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5a" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6a" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -60,9 +59,6 @@
   </si>
   <si>
     <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4</t>
   </si>
   <si>
     <t xml:space="preserve">5a</t>
@@ -855,475 +851,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>44302.5167824074</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="n">
-        <v>295.076646158839</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.179837618403249</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1694.475</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-315645.374999998</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.417138370185831</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.46993483862331</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.379719860037791</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>44386.5424768519</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1448.9446249588</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.636332243488483</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1380.315</v>
-      </c>
-      <c r="F3" t="n">
-        <v>69413.55</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.00501814443023</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.16105178813896</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.00217390250754501</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>44589.6049768519</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="n">
-        <v>60.3287312566173</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.170235193503023</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4972.755</v>
-      </c>
-      <c r="F4" t="n">
-        <v>934754.775</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.146687555132332</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.78052419198234</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.833606729828269</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>44665.4653819444</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="n">
-        <v>162.880436874946</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.10084878394279</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3376.71</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1004487.075</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.213339383042403</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.21186892551499</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.670928965182588</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>44733.6407291667</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.42175314548935</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.0381279127314033</v>
-      </c>
-      <c r="E6" t="n">
-        <v>29224.785</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9581164.725</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0267727103151798</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.534248675158665</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-1.57230766111248</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>44817.5355208333</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="n">
-        <v>184.844022452387</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-110.209228071763</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2434.48500000001</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-726.749999989534</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.213007658894106</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.26680541077648</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.671604780807045</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>44879.5539351852</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="n">
-        <v>16.9811082744574</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.13597861546666</v>
-      </c>
-      <c r="E8" t="n">
-        <v>20611.14</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3076999.575</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.080978032976474</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.22996603112432</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-1.09163277681234</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>44953.63375</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.57730895949344</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0193465004159673</v>
-      </c>
-      <c r="E9" t="n">
-        <v>63399.12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>63902143.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0322295008782968</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.197916770222312</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-1.49174642013085</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>44999.4580902778</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="n">
-        <v>17.0380754130775</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.0320683913904686</v>
-      </c>
-      <c r="E10" t="n">
-        <v>11738.415</v>
-      </c>
-      <c r="F10" t="n">
-        <v>12079423.95</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.146809310279103</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.23142053616508</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.833246401677268</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>45231.6105324074</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="n">
-        <v>26.7355374110375</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.216314895846472</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1870.17</v>
-      </c>
-      <c r="F11" t="n">
-        <v>131412.975</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.1019830414486</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.42708891827748</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.991472040175493</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>45296.6077083333</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="n">
-        <v>160.293015632576</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.141373916508917</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2495.43</v>
-      </c>
-      <c r="F12" t="n">
-        <v>511887</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.304619300450722</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.20491459947009</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.51624258355513</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>45331.5028703704</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13" t="n">
-        <v>3919.605</v>
-      </c>
-      <c r="F13" t="n">
-        <v>519994.725</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.262140092531933</v>
-      </c>
-      <c r="H13"/>
-      <c r="I13" t="n">
-        <v>-0.581466551606639</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>45376.6452083333</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="n">
-        <v>66.9517265176476</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.121519936802292</v>
-      </c>
-      <c r="E14" t="n">
-        <v>9708.4875</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2316871.9875</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.192172782267643</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.82576178086138</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-0.716308122120189</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>45527.554537037</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="n">
-        <v>31.8450445607709</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.268117748249557</v>
-      </c>
-      <c r="E15" t="n">
-        <v>31402.06</v>
-      </c>
-      <c r="F15" t="n">
-        <v>7027224.465</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.223306204924098</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.50304186093037</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.651099209186256</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>45548.5673611111</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="n">
-        <v>373.83163595079</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.294700163507004</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2675.001</v>
-      </c>
-      <c r="F16" t="n">
-        <v>807855.3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.250826695779266</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.57267605128971</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.600626242910576</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -2402,28 +1929,287 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45999.4979398148</v>
+        <v>44299.4938657407</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>10.244164539722</v>
+        <v>23.2169121274701</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0255811079414624</v>
+        <v>0.0291436573977775</v>
       </c>
       <c r="E2" t="n">
-        <v>9761.65499999999</v>
+        <v>4307.205</v>
       </c>
       <c r="F2" t="n">
-        <v>3167248.91999999</v>
-      </c>
-      <c r="G2"/>
+        <v>2660259.45</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.529921302115331</v>
+      </c>
       <c r="H2" t="n">
-        <v>1.01047654540352</v>
-      </c>
-      <c r="I2"/>
+        <v>1.365804457643</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.275788622087497</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>44386.4313657407</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>270.901397309407</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.243913614787338</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3691.38</v>
+      </c>
+      <c r="F3" t="n">
+        <v>405590.25</v>
+      </c>
+      <c r="G3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.43281124512988</v>
+      </c>
+      <c r="I3" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>44452.4125231481</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.96604019451215</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0337409970566135</v>
+      </c>
+      <c r="E4" t="n">
+        <v>25431.83</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4145552.2125</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.47844128219725</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.293592392476986</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.320171354402254</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>44510.6486805556</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21.1919407049499</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.028001747500781</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9437.55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5224032</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.544351728703457</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.32617073013491</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.264120393548061</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>44589.5744212963</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="n">
+        <v>139.607284708116</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00959627710876</v>
+      </c>
+      <c r="E6" t="n">
+        <v>716.295000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>612072.675000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.503157328132838</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.14490808036447</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.298296197734207</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>44659.4698958333</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10.1562152863735</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0162297983932237</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19692.375</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12133468.65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.53378538938896</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.00673189825654</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.272633317762059</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>44806.5677777778</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35.1860086355262</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0603196236104491</v>
+      </c>
+      <c r="E8" t="n">
+        <v>22736.31</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9536343.375</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.578629035198701</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.54637000494604</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.237599777549088</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>45140.4841435185</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="n">
+        <v>144.908635105566</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.12066224441846</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5865.765</v>
+      </c>
+      <c r="F9" t="n">
+        <v>875035.6875</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.693687349344395</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.16109426585046</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.158836225581222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>45197.4275347222</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18.6132002489516</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0385079170266907</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10745.0625</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5580703.05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.55420761962736</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.269821049701</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.256327507533635</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>45684.4465509259</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11" t="n">
+        <v>105280.575</v>
+      </c>
+      <c r="F11" t="n">
+        <v>75669084.285</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.519697920654582</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11" t="n">
+        <v>-0.28424902081433</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2467,286 +2253,396 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44299.4938657407</v>
+        <v>44292.6855324074</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>23.2169121274701</v>
+        <v>1376.47196470726</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0291436573977775</v>
+        <v>0.648509611554352</v>
       </c>
       <c r="E2" t="n">
-        <v>4307.205</v>
+        <v>1452.99</v>
       </c>
       <c r="F2" t="n">
-        <v>2660259.45</v>
+        <v>112025.325</v>
       </c>
       <c r="G2" t="n">
-        <v>0.529921302115331</v>
+        <v>0.776922527221678</v>
       </c>
       <c r="H2" t="n">
-        <v>1.365804457643</v>
+        <v>3.13876737032657</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.275788622087497</v>
+        <v>-0.109622285803481</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44386.4313657407</v>
+        <v>44452.6084490741</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>270.901397309407</v>
+        <v>163.514515592335</v>
       </c>
       <c r="D3" t="n">
-        <v>0.243913614787338</v>
+        <v>0.204434637572699</v>
       </c>
       <c r="E3" t="n">
-        <v>3691.38</v>
+        <v>6115.665</v>
       </c>
       <c r="F3" t="n">
-        <v>405590.25</v>
-      </c>
-      <c r="G3" t="e">
-        <v>#NUM!</v>
+        <v>1139762.025</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.456824240921209</v>
       </c>
       <c r="H3" t="n">
-        <v>2.43281124512988</v>
-      </c>
-      <c r="I3" t="e">
-        <v>#NUM!</v>
+        <v>2.21355631211454</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.340250858748654</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44452.4125231481</v>
+        <v>44589.6695601852</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>1.96604019451215</v>
+        <v>65.3921732107884</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0337409970566135</v>
+        <v>0.0942787293270622</v>
       </c>
       <c r="E4" t="n">
-        <v>25431.83</v>
+        <v>7646.175</v>
       </c>
       <c r="F4" t="n">
-        <v>4145552.2125</v>
+        <v>2076206.175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.47844128219725</v>
+        <v>0.38887615975603</v>
       </c>
       <c r="H4" t="n">
-        <v>0.293592392476986</v>
+        <v>1.81552577072827</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.320171354402254</v>
+        <v>-0.410188680672972</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44510.6486805556</v>
+        <v>44665.5667708333</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>21.1919407049499</v>
+        <v>33.6206498031091</v>
       </c>
       <c r="D5" t="n">
-        <v>0.028001747500781</v>
+        <v>0.135576128321251</v>
       </c>
       <c r="E5" t="n">
-        <v>9437.55</v>
+        <v>17846.175</v>
       </c>
       <c r="F5" t="n">
-        <v>5224032</v>
+        <v>3554067.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.544351728703457</v>
+        <v>0.315646469388177</v>
       </c>
       <c r="H5" t="n">
-        <v>1.32617073013491</v>
+        <v>1.52660610301117</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.264120393548061</v>
+        <v>-0.500799064039171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44589.5744212963</v>
+        <v>44817.6487152778</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>139.607284708116</v>
+        <v>1221.6724696109</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00959627710876</v>
+        <v>0.769787461283801</v>
       </c>
       <c r="E6" t="n">
-        <v>716.295000000001</v>
+        <v>1309.68</v>
       </c>
       <c r="F6" t="n">
-        <v>612072.675000001</v>
+        <v>71626.9499999976</v>
       </c>
       <c r="G6" t="n">
-        <v>0.503157328132838</v>
+        <v>0.810515482511753</v>
       </c>
       <c r="H6" t="n">
-        <v>2.14490808036447</v>
+        <v>3.08695478716117</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.298296197734207</v>
+        <v>-0.0912386848189221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44659.4698958333</v>
+        <v>44880.6008101852</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>10.1562152863735</v>
+        <v>20.830599317173</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0162297983932237</v>
+        <v>0.11282859276538</v>
       </c>
       <c r="E7" t="n">
-        <v>19692.375</v>
+        <v>9601.26</v>
       </c>
       <c r="F7" t="n">
-        <v>12133468.65</v>
+        <v>1616823.67499999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.53378538938896</v>
+        <v>0.183565739858753</v>
       </c>
       <c r="H7" t="n">
-        <v>1.00673189825654</v>
+        <v>1.31870176521404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.272633317762059</v>
+        <v>-0.736208370948997</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44806.5677777778</v>
+        <v>44953.5476388889</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>35.1860086355262</v>
+        <v>5.12392271126221</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0603196236104491</v>
+        <v>0.017662504410174</v>
       </c>
       <c r="E8" t="n">
-        <v>22736.31</v>
+        <v>19516.2975</v>
       </c>
       <c r="F8" t="n">
-        <v>9536343.375</v>
+        <v>27623910.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.578629035198701</v>
+        <v>0.119014868641982</v>
       </c>
       <c r="H8" t="n">
-        <v>1.54637000494604</v>
+        <v>0.709602570267519</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.237599777549088</v>
+        <v>-0.924398778390773</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45140.4841435185</v>
+        <v>44998.6080555556</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>144.908635105566</v>
+        <v>33.1477199133684</v>
       </c>
       <c r="D9" t="n">
-        <v>0.12066224441846</v>
+        <v>0.0959738782206115</v>
       </c>
       <c r="E9" t="n">
-        <v>5865.765</v>
+        <v>18100.7925</v>
       </c>
       <c r="F9" t="n">
-        <v>875035.6875</v>
+        <v>4526429.775</v>
       </c>
       <c r="G9" t="n">
-        <v>0.693687349344395</v>
+        <v>0.211055044837363</v>
       </c>
       <c r="H9" t="n">
-        <v>2.16109426585046</v>
+        <v>1.5204536605508</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.158836225581222</v>
+        <v>-0.675604262467908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45197.4275347222</v>
+        <v>45140.6931712963</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>18.6132002489516</v>
+        <v>660.196738628112</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0385079170266907</v>
+        <v>-0.520835073068891</v>
       </c>
       <c r="E10" t="n">
-        <v>10745.0625</v>
+        <v>1817.64</v>
       </c>
       <c r="F10" t="n">
-        <v>5580703.05</v>
+        <v>-73287.0000000003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.55420761962736</v>
+        <v>0.659625120007815</v>
       </c>
       <c r="H10" t="n">
-        <v>1.269821049701</v>
+        <v>2.81967337458485</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.256327507533635</v>
+        <v>-0.180702813802158</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45684.4465509259</v>
+        <v>45197.6053125</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11"/>
-      <c r="D11"/>
+      <c r="C11" t="n">
+        <v>129.083891621164</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0938164335971077</v>
+      </c>
       <c r="E11" t="n">
-        <v>105280.575</v>
+        <v>774.690000000004</v>
       </c>
       <c r="F11" t="n">
-        <v>75669084.285</v>
+        <v>290664.300000004</v>
       </c>
       <c r="G11" t="n">
-        <v>0.519697920654582</v>
-      </c>
-      <c r="H11"/>
+        <v>0.360986898896875</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.11087205003927</v>
+      </c>
       <c r="I11" t="n">
-        <v>-0.28424902081433</v>
+        <v>-0.442508559424093</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>45231.5688657407</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="n">
+        <v>17.4152616904298</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0461429737538231</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2871.045</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1505739.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.252976287770757</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.24093000476932</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.596920184646056</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>45296.6073611111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="n">
+        <v>236.595392304735</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.234697067244096</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2535.975</v>
+      </c>
+      <c r="F13" t="n">
+        <v>615902.774999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.447726779544469</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.37400628248923</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.348986928711107</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>45331.432037037</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14" t="n">
+        <v>47178.06</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17093496.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.346952867332309</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14" t="n">
+        <v>-0.459729519006806</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>45684.6125231481</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15" t="n">
+        <v>17617.44</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4829662.005</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.391295963011507</v>
+      </c>
+      <c r="H15"/>
+      <c r="I15" t="n">
+        <v>-0.407494632679106</v>
       </c>
     </row>
   </sheetData>
@@ -2791,396 +2687,257 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44292.6855324074</v>
+        <v>44292.6153935185</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>1376.47196470726</v>
+        <v>80.1792808720299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.648509611554352</v>
+        <v>0.0854043075688791</v>
       </c>
       <c r="E2" t="n">
-        <v>1452.99</v>
+        <v>2494.41</v>
       </c>
       <c r="F2" t="n">
-        <v>112025.325</v>
+        <v>756463.237499999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.776922527221678</v>
+        <v>0.364493365047336</v>
       </c>
       <c r="H2" t="n">
-        <v>3.13876737032657</v>
+        <v>1.90406215674476</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.109622285803481</v>
+        <v>-0.438310372831757</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44452.6084490741</v>
+        <v>44371.4813657407</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>163.514515592335</v>
+        <v>97.6891628527189</v>
       </c>
       <c r="D3" t="n">
-        <v>0.204434637572699</v>
+        <v>0.0853583962849015</v>
       </c>
       <c r="E3" t="n">
-        <v>6115.665</v>
+        <v>12283.86</v>
       </c>
       <c r="F3" t="n">
-        <v>1139762.025</v>
+        <v>5612459.475</v>
       </c>
       <c r="G3" t="n">
-        <v>0.456824240921209</v>
+        <v>0.428172659072591</v>
       </c>
       <c r="H3" t="n">
-        <v>2.21355631211454</v>
+        <v>1.98984638793256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.340250858748654</v>
+        <v>-0.368381067992078</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44589.6695601852</v>
+        <v>44452.6320601852</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>65.3921732107884</v>
+        <v>14.3008118570891</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0942787293270622</v>
+        <v>0.108622753028858</v>
       </c>
       <c r="E4" t="n">
-        <v>7646.175</v>
+        <v>13985.22</v>
       </c>
       <c r="F4" t="n">
-        <v>2076206.175</v>
+        <v>1879755.45</v>
       </c>
       <c r="G4" t="n">
-        <v>0.38887615975603</v>
+        <v>0.226952277503813</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81552577072827</v>
+        <v>1.15536069306266</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.410188680672972</v>
+        <v>-0.64406545468198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44665.5667708333</v>
+        <v>44517.6660763889</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>33.6206498031091</v>
+        <v>19.2526320754626</v>
       </c>
       <c r="D5" t="n">
-        <v>0.135576128321251</v>
+        <v>0.0781875702834405</v>
       </c>
       <c r="E5" t="n">
-        <v>17846.175</v>
+        <v>10388.19</v>
       </c>
       <c r="F5" t="n">
-        <v>3554067.6</v>
+        <v>2829969.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.315646469388177</v>
+        <v>0.258582477591671</v>
       </c>
       <c r="H5" t="n">
-        <v>1.52660610301117</v>
+        <v>1.2844901113878</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.500799064039171</v>
+        <v>-0.587400907696447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44817.6487152778</v>
+        <v>44589.6688657407</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>1221.6724696109</v>
+        <v>6.81656288449675</v>
       </c>
       <c r="D6" t="n">
-        <v>0.769787461283801</v>
+        <v>0.0283440749138616</v>
       </c>
       <c r="E6" t="n">
-        <v>1309.68</v>
+        <v>14670.15</v>
       </c>
       <c r="F6" t="n">
-        <v>71626.9499999976</v>
+        <v>4709921.4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.810515482511753</v>
+        <v>0.185682797933314</v>
       </c>
       <c r="H6" t="n">
-        <v>3.08695478716117</v>
+        <v>0.833565445540546</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0912386848189221</v>
+        <v>-0.731228328401752</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44880.6008101852</v>
+        <v>44665.5674652778</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>20.830599317173</v>
+        <v>5.52933269524834</v>
       </c>
       <c r="D7" t="n">
-        <v>0.11282859276538</v>
+        <v>0.0865643214300721</v>
       </c>
       <c r="E7" t="n">
-        <v>9601.26</v>
+        <v>18085.365</v>
       </c>
       <c r="F7" t="n">
-        <v>1616823.67499999</v>
+        <v>2548872.9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.183565739858753</v>
+        <v>0.208354964652513</v>
       </c>
       <c r="H7" t="n">
-        <v>1.31870176521404</v>
+        <v>0.742672721854738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.736208370948997</v>
+        <v>-0.681196146776164</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44953.5476388889</v>
+        <v>44818.4938657407</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>5.12392271126221</v>
+        <v>52.7801968701343</v>
       </c>
       <c r="D8" t="n">
-        <v>0.017662504410174</v>
+        <v>0.0495486591948861</v>
       </c>
       <c r="E8" t="n">
-        <v>19516.2975</v>
+        <v>7578.6</v>
       </c>
       <c r="F8" t="n">
-        <v>27623910.3</v>
+        <v>3395549.4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.119014868641982</v>
+        <v>0.333233531346469</v>
       </c>
       <c r="H8" t="n">
-        <v>0.709602570267519</v>
+        <v>1.72247100580547</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.924398778390773</v>
+        <v>-0.477251304546015</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44998.6080555556</v>
+        <v>45279.5674768519</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>33.1477199133684</v>
+        <v>406.643538815396</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0959738782206115</v>
+        <v>0.0913138679960434</v>
       </c>
       <c r="E9" t="n">
-        <v>18100.7925</v>
+        <v>1967.325</v>
       </c>
       <c r="F9" t="n">
-        <v>4526429.775</v>
+        <v>452437.575000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.211055044837363</v>
+        <v>0.586132065900496</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5204536605508</v>
+        <v>2.60921387615882</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.675604262467908</v>
+        <v>-0.232004518743436</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45140.6931712963</v>
+        <v>45684.582662037</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="n">
-        <v>660.196738628112</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.520835073068891</v>
-      </c>
+      <c r="C10"/>
+      <c r="D10"/>
       <c r="E10" t="n">
-        <v>1817.64</v>
+        <v>70079.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-73287.0000000003</v>
+        <v>24480940.185</v>
       </c>
       <c r="G10" t="n">
-        <v>0.659625120007815</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.81967337458485</v>
-      </c>
+        <v>0.294833100435432</v>
+      </c>
+      <c r="H10"/>
       <c r="I10" t="n">
-        <v>-0.180702813802158</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>45197.6053125</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="n">
-        <v>129.083891621164</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.0938164335971077</v>
-      </c>
-      <c r="E11" t="n">
-        <v>774.690000000004</v>
-      </c>
-      <c r="F11" t="n">
-        <v>290664.300000004</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.360986898896875</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.11087205003927</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.442508559424093</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>45231.5688657407</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="n">
-        <v>17.4152616904298</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0461429737538231</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2871.045</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1505739.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.252976287770757</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.24093000476932</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.596920184646056</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>45296.6073611111</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" t="n">
-        <v>236.595392304735</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.234697067244096</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2535.975</v>
-      </c>
-      <c r="F13" t="n">
-        <v>615902.774999999</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.447726779544469</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.37400628248923</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.348986928711107</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>45331.432037037</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14" t="n">
-        <v>47178.06</v>
-      </c>
-      <c r="F14" t="n">
-        <v>17093496.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.346952867332309</v>
-      </c>
-      <c r="H14"/>
-      <c r="I14" t="n">
-        <v>-0.459729519006806</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>45684.6125231481</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15" t="n">
-        <v>17617.44</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4829662.005</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.391295963011507</v>
-      </c>
-      <c r="H15"/>
-      <c r="I15" t="n">
-        <v>-0.407494632679106</v>
+        <v>-0.530423760536601</v>
       </c>
     </row>
   </sheetData>
@@ -3225,257 +2982,286 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44292.6153935185</v>
+        <v>44292.5445601852</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>80.1792808720299</v>
+        <v>110.528991754537</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0854043075688791</v>
+        <v>0.0582572824404321</v>
       </c>
       <c r="E2" t="n">
-        <v>2494.41</v>
+        <v>2261.85</v>
       </c>
       <c r="F2" t="n">
-        <v>756463.237499999</v>
+        <v>1479239.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.364493365047336</v>
+        <v>0.365076636764844</v>
       </c>
       <c r="H2" t="n">
-        <v>1.90406215674476</v>
+        <v>2.04347620840636</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.438310372831757</v>
+        <v>-0.437615959021695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44371.4813657407</v>
+        <v>44371.5931712963</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>97.6891628527189</v>
+        <v>145.261215981639</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0853583962849015</v>
+        <v>0.0887009145456758</v>
       </c>
       <c r="E3" t="n">
-        <v>12283.86</v>
+        <v>4130.49</v>
       </c>
       <c r="F3" t="n">
-        <v>5612459.475</v>
+        <v>1634483.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.428172659072591</v>
+        <v>0.402978589290512</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98984638793256</v>
+        <v>2.1621496753197</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.368381067992078</v>
+        <v>-0.394718027804303</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44452.6320601852</v>
+        <v>44452.5466435185</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>14.3008118570891</v>
+        <v>19.0096721211752</v>
       </c>
       <c r="D4" t="n">
-        <v>0.108622753028858</v>
+        <v>0.115018374888459</v>
       </c>
       <c r="E4" t="n">
-        <v>13985.22</v>
+        <v>7890.72</v>
       </c>
       <c r="F4" t="n">
-        <v>1879755.45</v>
+        <v>1001618.325</v>
       </c>
       <c r="G4" t="n">
-        <v>0.226952277503813</v>
+        <v>0.20773763726534</v>
       </c>
       <c r="H4" t="n">
-        <v>1.15536069306266</v>
+        <v>1.27897462621882</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.64406545468198</v>
+        <v>-0.682484812199451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44517.6660763889</v>
+        <v>44517.5244097222</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>19.2526320754626</v>
+        <v>17.0734960650927</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0781875702834405</v>
+        <v>0.0467154226076758</v>
       </c>
       <c r="E5" t="n">
-        <v>10388.19</v>
+        <v>11714.0625</v>
       </c>
       <c r="F5" t="n">
-        <v>2829969.6</v>
+        <v>10305974.8125</v>
       </c>
       <c r="G5" t="n">
-        <v>0.258582477591671</v>
+        <v>0.18568387517109</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2844901113878</v>
+        <v>1.23232245880176</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.587400907696447</v>
+        <v>-0.731225808851906</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44589.6688657407</v>
+        <v>44589.4438657407</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>6.81656288449675</v>
+        <v>4.49710858403589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0283440749138616</v>
+        <v>0.0449514608738104</v>
       </c>
       <c r="E6" t="n">
-        <v>14670.15</v>
+        <v>11118.255</v>
       </c>
       <c r="F6" t="n">
-        <v>4709921.4</v>
+        <v>2102382.5625</v>
       </c>
       <c r="G6" t="n">
-        <v>0.185682797933314</v>
+        <v>0.154310511172043</v>
       </c>
       <c r="H6" t="n">
-        <v>0.833565445540546</v>
+        <v>0.652933373865094</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.731228328401752</v>
+        <v>-0.811604490083723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44665.5674652778</v>
+        <v>44666.5452546296</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>5.52933269524834</v>
+        <v>2.88754040751858</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0865643214300721</v>
+        <v>0.0253800440355002</v>
       </c>
       <c r="E7" t="n">
-        <v>18085.365</v>
+        <v>17315.775</v>
       </c>
       <c r="F7" t="n">
-        <v>2548872.9</v>
+        <v>11257281</v>
       </c>
       <c r="G7" t="n">
-        <v>0.208354964652513</v>
+        <v>0.135702278222738</v>
       </c>
       <c r="H7" t="n">
-        <v>0.742672721854738</v>
+        <v>0.46052807035113</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.681196146776164</v>
+        <v>-0.867412861174027</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44818.4938657407</v>
+        <v>44818.6133101852</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>52.7801968701343</v>
+        <v>105.368942767542</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0495486591948861</v>
+        <v>0.144330317918993</v>
       </c>
       <c r="E8" t="n">
-        <v>7578.6</v>
+        <v>7592.37</v>
       </c>
       <c r="F8" t="n">
-        <v>3395549.4</v>
+        <v>2230414.875</v>
       </c>
       <c r="G8" t="n">
-        <v>0.333233531346469</v>
+        <v>0.355225529189463</v>
       </c>
       <c r="H8" t="n">
-        <v>1.72247100580547</v>
+        <v>2.02271262252492</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.477251304546015</v>
+        <v>-0.449495830090235</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45279.5674768519</v>
+        <v>44966.4577546296</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>406.643538815396</v>
+        <v>7.66440336835198</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0913138679960434</v>
+        <v>0.0131811634365342</v>
       </c>
       <c r="E9" t="n">
-        <v>1967.325</v>
+        <v>6523.66500000001</v>
       </c>
       <c r="F9" t="n">
-        <v>452437.575000001</v>
+        <v>6928926.30000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.586132065900496</v>
+        <v>0.110887957954024</v>
       </c>
       <c r="H9" t="n">
-        <v>2.60921387615882</v>
+        <v>0.88447835306939</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.232004518743436</v>
+        <v>-0.955115614158115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45684.582662037</v>
+        <v>44998.5250694444</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10"/>
-      <c r="D10"/>
+      <c r="C10" t="n">
+        <v>125.026099198208</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.158934750191826</v>
+      </c>
       <c r="E10" t="n">
-        <v>70079.1</v>
+        <v>3999.165</v>
       </c>
       <c r="F10" t="n">
-        <v>24480940.185</v>
+        <v>704544.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.294833100435432</v>
-      </c>
-      <c r="H10"/>
+        <v>0.338755228520558</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.097000681445</v>
+      </c>
       <c r="I10" t="n">
-        <v>-0.530423760536601</v>
+        <v>-0.470113992943802</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>45684.5284953704</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11" t="n">
+        <v>32923.56</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6246297.675</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.327860796281033</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11" t="n">
+        <v>-0.484310510676503</v>
       </c>
     </row>
   </sheetData>
@@ -3520,286 +3306,431 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44292.5445601852</v>
+        <v>44302.5167824074</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>110.528991754537</v>
+        <v>295.076646158839</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0582572824404321</v>
+        <v>-0.179837618403249</v>
       </c>
       <c r="E2" t="n">
-        <v>2261.85</v>
+        <v>1694.475</v>
       </c>
       <c r="F2" t="n">
-        <v>1479239.7</v>
+        <v>-315645.374999998</v>
       </c>
       <c r="G2" t="n">
-        <v>0.365076636764844</v>
+        <v>0.417138370185831</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04347620840636</v>
+        <v>2.46993483862331</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.437615959021695</v>
+        <v>-0.379719860037791</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44371.5931712963</v>
+        <v>44386.5424768519</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>145.261215981639</v>
+        <v>1448.9446249588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0887009145456758</v>
+        <v>0.636332243488483</v>
       </c>
       <c r="E3" t="n">
-        <v>4130.49</v>
+        <v>1380.315</v>
       </c>
       <c r="F3" t="n">
-        <v>1634483.7</v>
+        <v>69413.55</v>
       </c>
       <c r="G3" t="n">
-        <v>0.402978589290512</v>
+        <v>1.00501814443023</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1621496753197</v>
+        <v>3.16105178813896</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.394718027804303</v>
+        <v>0.00217390250754501</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44452.5466435185</v>
+        <v>44589.6049768519</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>19.0096721211752</v>
+        <v>60.3287312566173</v>
       </c>
       <c r="D4" t="n">
-        <v>0.115018374888459</v>
+        <v>0.170235193503023</v>
       </c>
       <c r="E4" t="n">
-        <v>7890.72</v>
+        <v>4972.755</v>
       </c>
       <c r="F4" t="n">
-        <v>1001618.325</v>
+        <v>934754.775</v>
       </c>
       <c r="G4" t="n">
-        <v>0.20773763726534</v>
+        <v>0.146687555132332</v>
       </c>
       <c r="H4" t="n">
-        <v>1.27897462621882</v>
+        <v>1.78052419198234</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.682484812199451</v>
+        <v>-0.833606729828269</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44517.5244097222</v>
+        <v>44665.4653819444</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>17.0734960650927</v>
+        <v>162.880436874946</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0467154226076758</v>
+        <v>0.10084878394279</v>
       </c>
       <c r="E5" t="n">
-        <v>11714.0625</v>
+        <v>3376.71</v>
       </c>
       <c r="F5" t="n">
-        <v>10305974.8125</v>
+        <v>1004487.075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.18568387517109</v>
+        <v>0.213339383042403</v>
       </c>
       <c r="H5" t="n">
-        <v>1.23232245880176</v>
+        <v>2.21186892551499</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.731225808851906</v>
+        <v>-0.670928965182588</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44589.4438657407</v>
+        <v>44733.6407291667</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>4.49710858403589</v>
+        <v>3.42175314548935</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0449514608738104</v>
+        <v>0.0381279127314033</v>
       </c>
       <c r="E6" t="n">
-        <v>11118.255</v>
+        <v>29224.785</v>
       </c>
       <c r="F6" t="n">
-        <v>2102382.5625</v>
+        <v>9581164.725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.154310511172043</v>
+        <v>0.0267727103151798</v>
       </c>
       <c r="H6" t="n">
-        <v>0.652933373865094</v>
+        <v>0.534248675158665</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.811604490083723</v>
+        <v>-1.57230766111248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44666.5452546296</v>
+        <v>44817.5355208333</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>2.88754040751858</v>
+        <v>184.844022452387</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0253800440355002</v>
+        <v>-110.209228071763</v>
       </c>
       <c r="E7" t="n">
-        <v>17315.775</v>
+        <v>2434.48500000001</v>
       </c>
       <c r="F7" t="n">
-        <v>11257281</v>
+        <v>-726.749999989534</v>
       </c>
       <c r="G7" t="n">
-        <v>0.135702278222738</v>
+        <v>0.213007658894106</v>
       </c>
       <c r="H7" t="n">
-        <v>0.46052807035113</v>
+        <v>2.26680541077648</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.867412861174027</v>
+        <v>-0.671604780807045</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44818.6133101852</v>
+        <v>44879.5539351852</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>105.368942767542</v>
+        <v>16.9811082744574</v>
       </c>
       <c r="D8" t="n">
-        <v>0.144330317918993</v>
+        <v>0.13597861546666</v>
       </c>
       <c r="E8" t="n">
-        <v>7592.37</v>
+        <v>20611.14</v>
       </c>
       <c r="F8" t="n">
-        <v>2230414.875</v>
+        <v>3076999.575</v>
       </c>
       <c r="G8" t="n">
-        <v>0.355225529189463</v>
+        <v>0.080978032976474</v>
       </c>
       <c r="H8" t="n">
-        <v>2.02271262252492</v>
+        <v>1.22996603112432</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.449495830090235</v>
+        <v>-1.09163277681234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44966.4577546296</v>
+        <v>44953.63375</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>7.66440336835198</v>
+        <v>1.57730895949344</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0131811634365342</v>
+        <v>0.0193465004159673</v>
       </c>
       <c r="E9" t="n">
-        <v>6523.66500000001</v>
+        <v>63399.12</v>
       </c>
       <c r="F9" t="n">
-        <v>6928926.30000001</v>
+        <v>63902143.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.110887957954024</v>
+        <v>0.0322295008782968</v>
       </c>
       <c r="H9" t="n">
-        <v>0.88447835306939</v>
+        <v>0.197916770222312</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.955115614158115</v>
+        <v>-1.49174642013085</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44998.5250694444</v>
+        <v>44999.4580902778</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>125.026099198208</v>
+        <v>17.0380754130775</v>
       </c>
       <c r="D10" t="n">
-        <v>0.158934750191826</v>
+        <v>0.0320683913904686</v>
       </c>
       <c r="E10" t="n">
-        <v>3999.165</v>
+        <v>11738.415</v>
       </c>
       <c r="F10" t="n">
-        <v>704544.6</v>
+        <v>12079423.95</v>
       </c>
       <c r="G10" t="n">
-        <v>0.338755228520558</v>
+        <v>0.146809310279103</v>
       </c>
       <c r="H10" t="n">
-        <v>2.097000681445</v>
+        <v>1.23142053616508</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.470113992943802</v>
+        <v>-0.833246401677268</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45684.5284953704</v>
+        <v>45231.6105324074</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11"/>
-      <c r="D11"/>
+      <c r="C11" t="n">
+        <v>26.7355374110375</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.216314895846472</v>
+      </c>
       <c r="E11" t="n">
-        <v>32923.56</v>
+        <v>1870.17</v>
       </c>
       <c r="F11" t="n">
-        <v>6246297.675</v>
+        <v>131412.975</v>
       </c>
       <c r="G11" t="n">
-        <v>0.327860796281033</v>
-      </c>
-      <c r="H11"/>
+        <v>0.1019830414486</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.42708891827748</v>
+      </c>
       <c r="I11" t="n">
-        <v>-0.484310510676503</v>
+        <v>-0.991472040175493</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>45296.6077083333</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="n">
+        <v>160.293015632576</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.141373916508917</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2495.43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>511887</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.304619300450722</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.20491459947009</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.51624258355513</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>45331.5028703704</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" t="n">
+        <v>3919.605</v>
+      </c>
+      <c r="F13" t="n">
+        <v>519994.725</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.262140092531933</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13" t="n">
+        <v>-0.581466551606639</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>45376.6452083333</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>66.9517265176476</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.121519936802292</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9708.4875</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2316871.9875</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.192172782267643</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.82576178086138</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.716308122120189</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>45527.554537037</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="n">
+        <v>31.8450445607709</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.268117748249557</v>
+      </c>
+      <c r="E15" t="n">
+        <v>31402.06</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7027224.465</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.223306204924098</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.50304186093037</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.651099209186256</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>45548.5673611111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="n">
+        <v>373.83163595079</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.294700163507004</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2675.001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>807855.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.250826695779266</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.57267605128971</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.600626242910576</v>
       </c>
     </row>
   </sheetData>
